--- a/survey_templates/045_self_mastery_course_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/045_self_mastery_course_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'relevant_and_well-organized'}</t>
+          <t>relevant_and_well-organized</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Relevant and Well-Organized'}</t>
+          <t>Relevant and Well-Organized</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'relevant_but_not_well-organized'}</t>
+          <t>relevant_but_not_well-organized</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Relevant but not Well-Organized'}</t>
+          <t>Relevant but not Well-Organized</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_relevant'}</t>
+          <t>somewhat_relevant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Relevant'}</t>
+          <t>Somewhat Relevant</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_irrelevant'}</t>
+          <t>somewhat_irrelevant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Irrelevant'}</t>
+          <t>Somewhat Irrelevant</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
